--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008511962878429835</v>
       </c>
       <c r="C2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>43869580</v>
+        <v>4071012</v>
       </c>
       <c r="L2" t="n">
-        <v>23549672</v>
+        <v>1722422</v>
       </c>
       <c r="M2" t="n">
-        <v>5469217</v>
+        <v>305601</v>
       </c>
       <c r="N2" t="n">
-        <v>242383</v>
+        <v>7039</v>
       </c>
       <c r="O2" t="n">
-        <v>3232373</v>
+        <v>186300</v>
       </c>
       <c r="P2" t="n">
-        <v>1227467</v>
+        <v>37003</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999307990074158</v>
+        <v>0.9999334812164307</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8443630337715149</v>
+        <v>0.7293843626976013</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7191070914268494</v>
+        <v>0.5535507798194885</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6548300981521606</v>
+        <v>0.4302815198898315</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2453048229217529</v>
+        <v>0.05050874873995781</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7003276944160461</v>
+        <v>0.447798877954483</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8173245787620544</v>
+        <v>0.6430160403251648</v>
       </c>
       <c r="X2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559409618377686</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116660952568054</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582287430763245</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617533564567566</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902009129524231</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039737086905555</v>
       </c>
       <c r="C3" t="n">
-        <v>3146</v>
+        <v>380</v>
       </c>
       <c r="D3" t="n">
-        <v>43869580</v>
+        <v>4071012</v>
       </c>
       <c r="E3" t="n">
-        <v>6023136</v>
+        <v>850741</v>
       </c>
       <c r="F3" t="n">
-        <v>155790</v>
+        <v>32271</v>
       </c>
       <c r="G3" t="n">
-        <v>13716</v>
+        <v>3070</v>
       </c>
       <c r="H3" t="n">
-        <v>9842</v>
+        <v>2534</v>
       </c>
       <c r="I3" t="n">
-        <v>530</v>
+        <v>104</v>
       </c>
       <c r="J3" t="n">
-        <v>100161852</v>
+        <v>10016202</v>
       </c>
       <c r="K3" t="n">
-        <v>105134011</v>
+        <v>9859064</v>
       </c>
       <c r="L3" t="n">
-        <v>121287860</v>
+        <v>11621302</v>
       </c>
       <c r="M3" t="n">
-        <v>151060548</v>
+        <v>14983110</v>
       </c>
       <c r="N3" t="n">
-        <v>161656730</v>
+        <v>16107469</v>
       </c>
       <c r="O3" t="n">
-        <v>156812428</v>
+        <v>15587956</v>
       </c>
       <c r="P3" t="n">
-        <v>161087043</v>
+        <v>16115252</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8760645389556885</v>
+        <v>0.8207499980926514</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7177738547325134</v>
+        <v>0.5189374685287476</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5847833156585693</v>
+        <v>0.3244667947292328</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2712542116641998</v>
+        <v>0.07837831974029541</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6337451934814453</v>
+        <v>0.3639318645000458</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6344767808914185</v>
+        <v>0.1909290254116058</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1972670</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84826</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>68106</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100166220</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>111010280</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127594505</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152619092</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>162100491</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157696105</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>161228809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575406908988953</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097784161567688</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85721355676651</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661096453666687</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014128446578979</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0321438545796774</v>
       </c>
       <c r="C4" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>7487213</v>
+        <v>1363190</v>
       </c>
       <c r="E4" t="n">
-        <v>23549672</v>
+        <v>1722422</v>
       </c>
       <c r="F4" t="n">
-        <v>1508505</v>
+        <v>180760</v>
       </c>
       <c r="G4" t="n">
-        <v>92651</v>
+        <v>19971</v>
       </c>
       <c r="H4" t="n">
-        <v>156922</v>
+        <v>30878</v>
       </c>
       <c r="I4" t="n">
-        <v>14253</v>
+        <v>1909</v>
       </c>
       <c r="J4" t="n">
-        <v>4368</v>
+        <v>420</v>
       </c>
       <c r="K4" t="n">
-        <v>8086249</v>
+        <v>1510424</v>
       </c>
       <c r="L4" t="n">
-        <v>9198820</v>
+        <v>1389166</v>
       </c>
       <c r="M4" t="n">
-        <v>2882899</v>
+        <v>404634</v>
       </c>
       <c r="N4" t="n">
-        <v>745706</v>
+        <v>132323</v>
       </c>
       <c r="O4" t="n">
-        <v>1383142</v>
+        <v>229735</v>
       </c>
       <c r="P4" t="n">
-        <v>274344</v>
+        <v>20543</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999653697013855</v>
+        <v>0.9999667406082153</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8599217534065247</v>
+        <v>0.7723746299743652</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7184398174285889</v>
+        <v>0.5356855392456055</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6178276538848877</v>
+        <v>0.3699565827846527</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2576277554035187</v>
+        <v>0.06143038347363472</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6653749346733093</v>
+        <v>0.4015328586101532</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7143862843513489</v>
+        <v>0.2944329082965851</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2063963</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>828823</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55262</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11381</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2209980</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2892175</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1324355</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301945</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499465</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567400813102722</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107212424278259</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577207922935486</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614247560501099</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017109274864197</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>629</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>423454</v>
+        <v>108820</v>
       </c>
       <c r="E5" t="n">
-        <v>2599450</v>
+        <v>411251</v>
       </c>
       <c r="F5" t="n">
-        <v>5469217</v>
+        <v>305601</v>
       </c>
       <c r="G5" t="n">
-        <v>230448</v>
+        <v>35141</v>
       </c>
       <c r="H5" t="n">
-        <v>572967</v>
+        <v>74779</v>
       </c>
       <c r="I5" t="n">
-        <v>56388</v>
+        <v>6258</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6206160</v>
+        <v>889100</v>
       </c>
       <c r="L5" t="n">
-        <v>9259648</v>
+        <v>1596710</v>
       </c>
       <c r="M5" t="n">
-        <v>3883336</v>
+        <v>636255</v>
       </c>
       <c r="N5" t="n">
-        <v>651181</v>
+        <v>82769</v>
       </c>
       <c r="O5" t="n">
-        <v>1868057</v>
+        <v>325609</v>
       </c>
       <c r="P5" t="n">
-        <v>707146</v>
+        <v>156802</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999732375144958</v>
+        <v>0.999974250793457</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9124754667282104</v>
+        <v>0.853056788444519</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8869631290435791</v>
+        <v>0.8171494603157043</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9585645794868469</v>
+        <v>0.936257541179657</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9914456605911255</v>
+        <v>0.986828088760376</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9800901412963867</v>
+        <v>0.9659915566444397</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9939895272254944</v>
+        <v>0.9891396760940552</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80454</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>857060</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99758</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291816</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2126182</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2960109</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1335418</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302832</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502837</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734460115432739</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641615152359009</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837119579315186</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962964653968811</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938620328903198</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983729124069214</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>138988</v>
+        <v>22803</v>
       </c>
       <c r="E6" t="n">
-        <v>193832</v>
+        <v>26080</v>
       </c>
       <c r="F6" t="n">
-        <v>224074</v>
+        <v>24874</v>
       </c>
       <c r="G6" t="n">
-        <v>242383</v>
+        <v>7039</v>
       </c>
       <c r="H6" t="n">
-        <v>85737</v>
+        <v>8418</v>
       </c>
       <c r="I6" t="n">
-        <v>8312</v>
+        <v>573</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65084</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53535</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109471</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69932</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>34679</v>
+        <v>14501</v>
       </c>
       <c r="E7" t="n">
-        <v>350918</v>
+        <v>91094</v>
       </c>
       <c r="F7" t="n">
-        <v>922021</v>
+        <v>147088</v>
       </c>
       <c r="G7" t="n">
-        <v>365519</v>
+        <v>61219</v>
       </c>
       <c r="H7" t="n">
-        <v>3232373</v>
+        <v>186300</v>
       </c>
       <c r="I7" t="n">
-        <v>194861</v>
+        <v>11699</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8100</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297921</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76159</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>192</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1915</v>
+        <v>1110</v>
       </c>
       <c r="E8" t="n">
-        <v>31484</v>
+        <v>10000</v>
       </c>
       <c r="F8" t="n">
-        <v>72509</v>
+        <v>19641</v>
       </c>
       <c r="G8" t="n">
-        <v>43372</v>
+        <v>12922</v>
       </c>
       <c r="H8" t="n">
-        <v>557674</v>
+        <v>113126</v>
       </c>
       <c r="I8" t="n">
-        <v>1227467</v>
+        <v>37003</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
